--- a/web/demo/2026-05_ledger_20260601-0903.xlsx
+++ b/web/demo/2026-05_ledger_20260601-0903.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FAF7F2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E5B45"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,69 +425,84 @@
   </sheetPr>
   <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>결제처</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>결제수단</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>결제구분</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>원거래통화</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>원거래금액</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>collect_status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>구매항목</t>
         </is>
@@ -524,8 +549,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -536,7 +559,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,8 +601,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -591,7 +611,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -634,8 +653,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -646,7 +663,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -674,7 +690,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -685,8 +700,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -697,7 +710,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -740,8 +752,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -752,7 +762,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -795,8 +804,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -807,7 +814,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,7 +841,6 @@
           <t>구독료</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -846,8 +851,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -858,7 +861,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -901,8 +903,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -913,7 +913,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -956,8 +955,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -968,7 +965,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -996,7 +992,6 @@
           <t>교육비</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1007,8 +1002,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1066,8 +1059,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1078,7 +1069,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1106,7 +1096,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -1117,8 +1106,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1129,7 +1116,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1172,8 +1158,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1184,7 +1168,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1227,8 +1210,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1239,7 +1220,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1267,7 +1247,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1278,8 +1257,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1290,7 +1267,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1333,8 +1309,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1345,7 +1319,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1388,8 +1361,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1400,7 +1371,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1443,8 +1413,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1455,7 +1423,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1483,7 +1450,6 @@
           <t>기타물품</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -1494,8 +1460,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1538,7 +1502,6 @@
           <t>소모품비</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>신한법인카드</t>
@@ -1549,8 +1512,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1628,7 +1589,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1671,8 +1631,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1683,7 +1641,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1726,8 +1683,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1738,7 +1693,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1766,7 +1720,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1777,8 +1730,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1789,7 +1740,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1832,8 +1782,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1844,7 +1792,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1887,8 +1834,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1899,7 +1844,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1927,7 +1871,6 @@
           <t>복리후생비</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>신한법인카드</t>
@@ -1938,8 +1881,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>receipt</t>
@@ -1997,8 +1938,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2009,7 +1948,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2037,7 +1975,6 @@
           <t>교통비</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -2048,8 +1985,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2060,7 +1995,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2103,8 +2037,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2115,7 +2047,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2143,7 +2074,6 @@
           <t>식대</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>우리카드</t>
@@ -2154,8 +2084,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2166,7 +2094,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2209,8 +2136,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>manual</t>
@@ -2221,7 +2146,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2264,8 +2188,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2276,7 +2198,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2304,7 +2225,6 @@
           <t>구독료</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>국민카드</t>
@@ -2315,8 +2235,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2327,7 +2245,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2370,8 +2287,6 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2382,7 +2297,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2425,8 +2339,6 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -2437,7 +2349,6 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
